--- a/apps/api/assets/vocabulary/初中/外研版/外研版初中英语七年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/外研版/外研版初中英语七年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D642"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -598,6 +598,16 @@
           <t>Miss</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>n. 女士，小姐，年轻未婚女子
@@ -658,6 +668,16 @@
           <t>good morning</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">int. （上午见面时用语，非正式场合常说 Morning）早上好
@@ -691,6 +711,16 @@
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>good afternoon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>I'm</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>abbr. 我是（缩写）</t>
@@ -787,6 +827,16 @@
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>I am</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1681,6 +1731,16 @@
           <t>What about ...?</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 不；…怎样
@@ -2117,6 +2177,16 @@
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>first name</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2157,6 +2227,16 @@
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>last name</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2933,6 +3013,16 @@
           <t>how old</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">conj. 多少岁
@@ -3760,6 +3850,16 @@
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>on the left</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -3824,6 +3924,16 @@
           <t>on the right</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在右边；在右侧；在右面</t>
@@ -3903,6 +4013,16 @@
       <c r="A151" s="2" t="inlineStr">
         <is>
           <t>next to</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -4648,6 +4768,16 @@
           <t>in English</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 用英语；用英语说；用英语表达</t>
@@ -5092,6 +5222,16 @@
           <t>of course</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 当然
@@ -5249,6 +5389,16 @@
           <t>You're welcome</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 不客气；别客气；不用谢</t>
@@ -5875,6 +6025,16 @@
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>how many</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -5938,6 +6098,16 @@
       <c r="A239" s="2" t="inlineStr">
         <is>
           <t>a lot of</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -7129,6 +7299,16 @@
           <t>let's</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
           <t>让我们（let us的简写）</t>
@@ -7139,6 +7319,16 @@
       <c r="A291" s="2" t="inlineStr">
         <is>
           <t>let us</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -7740,6 +7930,16 @@
           <t>go shopping</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 去买东西
@@ -7799,6 +7999,16 @@
       <c r="A320" s="2" t="inlineStr">
         <is>
           <t>have got</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -7863,6 +8073,16 @@
           <t>too much</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 太过份
@@ -7898,6 +8118,16 @@
       <c r="A325" s="2" t="inlineStr">
         <is>
           <t>lots of</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -7938,6 +8168,16 @@
           <t>How about ...?</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 怎么样；如何；怎麽样</t>
@@ -8275,6 +8515,16 @@
           <t>be good for</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 值…
@@ -8311,6 +8561,16 @@
       <c r="A344" s="2" t="inlineStr">
         <is>
           <t>be bad for</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -8498,6 +8758,16 @@
           <t>a bit</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 有点儿〔作副词用〕
@@ -8940,6 +9210,16 @@
       <c r="A371" s="2" t="inlineStr">
         <is>
           <t>o'clock</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -9401,6 +9681,16 @@
           <t>go to school</t>
         </is>
       </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 到校上课；上学去；开始求学
@@ -9602,6 +9892,16 @@
           <t>go home</t>
         </is>
       </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 回家；〈口〉死；(忠告等)刻骨铭心；击中
@@ -9661,6 +9961,16 @@
       <c r="A403" s="2" t="inlineStr">
         <is>
           <t>have dinner</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
@@ -9747,6 +10057,16 @@
           <t>go to bed</t>
         </is>
       </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 睡；同床；【印】付印
@@ -9782,6 +10102,16 @@
       <c r="A409" s="2" t="inlineStr">
         <is>
           <t>go to sleep</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
@@ -10530,6 +10860,16 @@
           <t>come from</t>
         </is>
       </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 来自；出身；归因于
@@ -10728,6 +11068,16 @@
       <c r="A450" s="2" t="inlineStr">
         <is>
           <t>look at</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
@@ -11117,6 +11467,16 @@
           <t>a little</t>
         </is>
       </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 一点
@@ -11271,6 +11631,16 @@
           <t>all over the world</t>
         </is>
       </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 遍及全世界
@@ -11427,6 +11797,16 @@
           <t>be good at</t>
         </is>
       </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 善于
@@ -11486,6 +11866,16 @@
       <c r="A484" s="2" t="inlineStr">
         <is>
           <t>many kinds of</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -12262,6 +12652,16 @@
           <t>search for</t>
         </is>
       </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 寻找；寻求；探求
@@ -12819,6 +13219,16 @@
           <t>ha ha</t>
         </is>
       </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. (造在花园界沟里不遮挡视线的)隐篱；哈哈的笑声；哈哈的笑声；〔美俚〕(对某人的)嘲笑
@@ -13255,6 +13665,16 @@
           <t>at weekends</t>
         </is>
       </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在周末；每逢周末；生在周末</t>
@@ -13316,6 +13736,16 @@
           <t>hear from</t>
         </is>
       </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 得到…的消息
@@ -13351,6 +13781,16 @@
           <t>I'm afraid</t>
         </is>
       </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
           <t>[口语]恐怕，担心；大概；对不起[因为要说不受欢迎的话而用的客套语]</t>
@@ -13361,6 +13801,16 @@
       <c r="A566" s="2" t="inlineStr">
         <is>
           <t>can't</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
@@ -13542,6 +13992,16 @@
           <t>take photos</t>
         </is>
       </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 照相；拍照；拍照片</t>
@@ -13579,6 +14039,16 @@
           <t>wait to</t>
         </is>
       </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -13666,6 +14136,16 @@
           <t>a few</t>
         </is>
       </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 几个；〔反语〕很多；〈俚〉一点点
@@ -13700,6 +14180,16 @@
       <c r="A582" s="2" t="inlineStr">
         <is>
           <t>on sale</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
@@ -13786,6 +14276,16 @@
           <t>go back</t>
         </is>
       </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “Come back”的变体；回来；追溯到；回顾
@@ -13847,6 +14347,16 @@
           <t>get off</t>
         </is>
       </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 下车；脱下(衣服等)；脱(衣)；下(马)
@@ -13858,6 +14368,16 @@
       <c r="A590" s="2" t="inlineStr">
         <is>
           <t>hot dog</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
@@ -14383,6 +14903,16 @@
           <t>get ready for</t>
         </is>
       </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 作准备
@@ -14439,6 +14969,16 @@
       <c r="A615" s="2" t="inlineStr">
         <is>
           <t>at the moment</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D615" s="2" t="inlineStr">
@@ -14480,6 +15020,16 @@
           <t>at work</t>
         </is>
       </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 做着；在工作；起着作用；运转中
@@ -14513,6 +15063,16 @@
       <c r="A619" s="2" t="inlineStr">
         <is>
           <t>put away</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D619" s="2" t="inlineStr">
@@ -14712,6 +15272,16 @@
       <c r="A628" s="2" t="inlineStr">
         <is>
           <t>sweep away</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D628" s="2" t="inlineStr">
@@ -14985,6 +15555,16 @@
           <t>Merry Christmas</t>
         </is>
       </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 圣诞快乐
